--- a/data/trans_orig/IP07KS_C09_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C09_2023-Provincia-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de ir bien en el colegio en 2023 (tasa de respuesta: 99,83%)</t>
+          <t>Menores según la frecuencia de ir bien en el colegio, percibida por el/la menor en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -833,64 +833,64 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1147</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>23272</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14710</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>33031</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>42,79%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>27,05%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>60,73%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>14129</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3509</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>28012</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>22,84%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,67%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>45,29%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24475</t>
+          <t>14750</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15804</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33738</t>
+          <t>20258</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38021</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18268</t>
+          <t>27793</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57154</t>
+          <t>49487</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>53,29%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>19445</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12071</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>26673</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>35,75%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>22,19%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>49,04%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>16978</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4968</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>32885</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>27,45%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>8,03%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>53,16%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20375</t>
+          <t>17098</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12399</t>
+          <t>11327</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28451</t>
+          <t>22820</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>37353</t>
+          <t>36543</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19581</t>
+          <t>27529</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53702</t>
+          <t>46496</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>50,07%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10694</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4243</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>22772</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>19,66%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>7,8%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>41,87%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>29180</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2705</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>51924</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>47,17%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,37%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>83,94%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11996</t>
+          <t>5047</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25542</t>
+          <t>13814</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>41176</t>
+          <t>15741</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13316</t>
+          <t>7123</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>77869</t>
+          <t>27905</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>980</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2547</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>359</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5630</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5685</t>
+          <t>6319</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -1854,107 +1854,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1154</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5931</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1227</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5538</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>9,59%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>14,39%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1227</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>8692</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1154</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>5904</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7118</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3730</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11090</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>31,76%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>16,64%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>49,48%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>7735</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4496</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>11265</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>37,07%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>21,55%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>53,98%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>7536</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12356</t>
+          <t>11499</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>15752</t>
+          <t>14654</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11017</t>
+          <t>10114</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21460</t>
+          <t>20183</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>46,65%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9045</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5852</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>13197</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>40,35%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>26,11%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>58,88%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>10064</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>6795</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>13614</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>48,22%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>32,56%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>65,23%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9873</t>
+          <t>10187</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>6286</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13868</t>
+          <t>13392</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>19937</t>
+          <t>19231</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15323</t>
+          <t>14036</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25247</t>
+          <t>24405</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>56,41%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4644</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2212</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>8606</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>20,72%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>9,87%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>38,4%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2515</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>5517</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>12,05%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>26,44%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5020</t>
+          <t>2531</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2468</t>
+          <t>650</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8845</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7535</t>
+          <t>7175</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12138</t>
+          <t>11452</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,47%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1607</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4250</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>7,17%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>18,96%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>555</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2275</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2966</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>10,9%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1759</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>4644</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>7,13%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2314</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>621</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>22414</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>22414</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>22414</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>24668</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24668</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24668</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>45537</t>
+          <t>43263</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>45537</t>
+          <t>43263</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>45537</t>
+          <t>43263</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,74 +2766,74 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>1619</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>61,11%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>5,01%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1849</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2938</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>62,92%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>19750</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>11</t>
@@ -2841,27 +2841,27 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>21369</t>
+          <t>19280</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16720</t>
+          <t>13921</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2879,107 +2879,107 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>1030</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2516</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>38,89%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1089</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2644</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>37,08%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>94,99%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>90,0%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1089</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>6448</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>5,35%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1030</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>5679</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>31,66%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>7784</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>4711</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>11128</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>38,38%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>23,22%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>54,86%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>9380</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>6521</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>11860</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>63,82%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>44,36%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>80,69%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>7738</t>
+          <t>9863</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4507</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11105</t>
+          <t>12264</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>17118</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13060</t>
+          <t>13645</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>21463</t>
+          <t>22301</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>62,19%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>11944</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>8637</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>15185</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>58,88%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>42,58%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>74,86%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>5318</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>2838</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>8177</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>36,18%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>19,31%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>55,64%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>11709</t>
+          <t>5711</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8398</t>
+          <t>3310</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14947</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>17026</t>
+          <t>17656</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12690</t>
+          <t>13079</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>21138</t>
+          <t>21667</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,42%</t>
         </is>
       </c>
     </row>
@@ -3674,107 +3674,107 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>556</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>2686</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>556</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>2732</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>13,44%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>2730</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4130,72 +4130,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>3688</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>1407</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>7229</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>18,96%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>7,23%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>37,17%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>5314</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>2578</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>8871</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>28,84%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>13,99%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>48,15%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>5579</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1696</t>
+          <t>2925</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7971</t>
+          <t>9288</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>9499</t>
+          <t>9267</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>14281</t>
+          <t>13764</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>35,46%</t>
         </is>
       </c>
     </row>
@@ -4243,72 +4243,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10040</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>6158</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>13886</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>51,61%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>31,66%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>71,39%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>5947</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>3390</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>9318</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>32,28%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>18,4%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>50,57%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>6137</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6179</t>
+          <t>3164</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14306</t>
+          <t>9571</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>16351</t>
+          <t>16176</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>11462</t>
+          <t>11346</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>21610</t>
+          <t>20581</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>53,03%</t>
         </is>
       </c>
     </row>
@@ -4356,72 +4356,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>3442</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>1229</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>6827</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>17,7%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>6,32%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>35,1%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>6107</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>3124</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>9450</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>33,14%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>16,96%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>51,29%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>3769</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>3410</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7637</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>9876</t>
+          <t>9899</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>14415</t>
+          <t>14697</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>37,86%</t>
         </is>
       </c>
     </row>
@@ -4469,72 +4469,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>1707</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>7502</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>8,78%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>38,57%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>1057</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>3249</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>5,74%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>1191</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3627</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>6,15%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>17,63%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>7489</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>9,48%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>613</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>10784</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>20,88%</t>
         </is>
       </c>
     </row>
@@ -4582,107 +4582,107 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>574</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2807</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>3377</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>3141</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>16,13%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>3019</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -4695,57 +4695,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>19451</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>19451</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>19451</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4812,72 +4812,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>24806</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>17576</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>31212</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>52,16%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>36,96%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>65,63%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>13417</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>8991</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>17603</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>49,16%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>32,94%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>64,49%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>24343</t>
+          <t>14225</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>17370</t>
+          <t>9187</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>31302</t>
+          <t>18982</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>37760</t>
+          <t>39032</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>29105</t>
+          <t>29628</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>46342</t>
+          <t>46673</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>61,09%</t>
         </is>
       </c>
     </row>
@@ -4925,72 +4925,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>8980</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>4503</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>15139</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>18,88%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>9,47%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>31,83%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>11145</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>6879</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>15647</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>40,83%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>25,2%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>57,33%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>8603</t>
+          <t>11798</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4487</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>14385</t>
+          <t>17068</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>19748</t>
+          <t>20778</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>13096</t>
+          <t>14050</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>27234</t>
+          <t>28363</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,12%</t>
         </is>
       </c>
     </row>
@@ -5038,72 +5038,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11014</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>5567</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>21401</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>23,16%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>11,71%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>45,0%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>2311</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>732</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>5901</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>8,47%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>21,62%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>10513</t>
+          <t>2453</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>760</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>19774</t>
+          <t>6377</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>12824</t>
+          <t>13467</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>6686</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>25647</t>
+          <t>25365</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -5151,107 +5151,107 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>801</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6905</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
+          <t>5,8%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>14,52%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>2682</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>804</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>7602</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>5,81%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>16,47%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7356</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -5264,107 +5264,107 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>2225</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>1715</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>8,15%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>5,95%</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>1718</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>1862</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>47558</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>47558</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>47558</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>27295</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>27295</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>27295</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>46141</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>46141</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>46141</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>73436</t>
+          <t>76401</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>73436</t>
+          <t>76401</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>73436</t>
+          <t>76401</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5494,72 +5494,72 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>55589</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>46956</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>63611</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>63,71%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>53,82%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>72,91%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>39419</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>32447</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>45798</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>62,07%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>51,09%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>72,12%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>51823</t>
+          <t>43904</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>43344</t>
+          <t>36661</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>59052</t>
+          <t>51034</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>91242</t>
+          <t>99493</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>79406</t>
+          <t>88137</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>101706</t>
+          <t>111057</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,45%</t>
         </is>
       </c>
     </row>
@@ -5607,72 +5607,72 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>30784</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>22904</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>39132</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>35,28%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>26,25%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>44,85%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>24085</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>17706</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>31057</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>37,93%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>27,88%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>48,91%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>28708</t>
+          <t>26489</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>21733</t>
+          <t>19359</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>37713</t>
+          <t>33732</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,22 +5682,22 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>52793</t>
+          <t>57273</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>42207</t>
+          <t>45937</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>64428</t>
+          <t>68341</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>43,35%</t>
         </is>
       </c>
     </row>
@@ -5720,107 +5720,107 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>876</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>4541</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>4431</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
-      <c r="S48" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T48" s="2" t="inlineStr">
-        <is>
-          <t>4748</t>
-        </is>
-      </c>
-      <c r="U48" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -6059,57 +6059,57 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>63504</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>63504</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>63504</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>70393</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>70393</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>70393</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>157642</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>157642</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>157642</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6176,72 +6176,72 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>139688</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>122386</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>159358</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>51,84%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>45,42%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>59,15%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>91014</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>60109</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>109311</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>43,24%</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>28,56%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>51,94%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>140331</t>
+          <t>97705</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>122068</t>
+          <t>85497</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>161101</t>
+          <t>110001</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>231345</t>
+          <t>237394</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>188453</t>
+          <t>214525</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>257901</t>
+          <t>261113</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>55,91%</t>
         </is>
       </c>
     </row>
@@ -6289,72 +6289,72 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>90894</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>75412</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>104945</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>33,73%</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>27,99%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>38,95%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>75741</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>47941</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>93094</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>35,99%</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>22,78%</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>44,23%</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>90412</t>
+          <t>79657</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>73725</t>
+          <t>67657</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>106617</t>
+          <t>91663</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>166154</t>
+          <t>170551</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>135002</t>
+          <t>148413</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>188261</t>
+          <t>190130</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>40,71%</t>
         </is>
       </c>
     </row>
@@ -6402,72 +6402,72 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>31227</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>20595</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>48641</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>11,59%</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>7,64%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>18,05%</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>40113</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>12588</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>101484</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>19,06%</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>5,98%</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>48,22%</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>32617</t>
+          <t>16487</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>20780</t>
+          <t>10239</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>51506</t>
+          <t>26351</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>72730</t>
+          <t>47714</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>44375</t>
+          <t>33956</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>153500</t>
+          <t>69302</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -6515,72 +6515,72 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>7052</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>3128</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>14823</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>528</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>5230</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>7440</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>599</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>15216</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>9468</t>
+          <t>9197</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>17657</t>
+          <t>16642</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -6628,72 +6628,72 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>2964</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>1576</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>7707</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>1594</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>7114</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>3,66%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>3100</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,27 +6703,27 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>563</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>7094</t>
+          <t>6885</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -6741,57 +6741,57 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>269435</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>269435</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>269435</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>271397</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>271397</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>271397</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>481869</t>
+          <t>467024</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>481869</t>
+          <t>467024</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>481869</t>
+          <t>467024</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
